--- a/data/transformed_data_2019.xlsx
+++ b/data/transformed_data_2019.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17547" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17541" uniqueCount="45">
   <si>
     <t>source</t>
   </si>
@@ -2369,7 +2369,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>729831.4143413941</v>
+        <v>743285.030741394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2705,7 +2705,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>80729.2836</v>
+        <v>69253.7188</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -2873,7 +2873,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>7925.691199999999</v>
+        <v>9903.7428</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -5109,7 +5109,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>16724.35494110953</v>
+        <v>16397.34854110953</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -5319,7 +5319,7 @@
         <v>4</v>
       </c>
       <c r="D146">
-        <v>8394.627262563079</v>
+        <v>11222.12552503551</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -5445,7 +5445,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>37.926</v>
+        <v>217.4424</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -5487,7 +5487,7 @@
         <v>4</v>
       </c>
       <c r="D158">
-        <v>14670.2753518485</v>
+        <v>17497.77361432092</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -5613,7 +5613,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>709.6376</v>
+        <v>562.1476</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -7835,7 +7835,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>18269.82771038407</v>
+        <v>18539.52371038407</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -8171,7 +8171,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>11243.7948</v>
+        <v>10955.5572</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -8339,7 +8339,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>7187.3984</v>
+        <v>7168.8568</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -10575,7 +10575,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>6638.046979231863</v>
+        <v>6244.459379231863</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -10911,7 +10911,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>742.5068</v>
+        <v>618.6152</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -11079,7 +11079,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>2007.5496</v>
+        <v>1490.0704</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -13315,7 +13315,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>12822.1599658606</v>
+        <v>15509.0063658606</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -13651,7 +13651,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>14536.6144</v>
+        <v>13232.8028</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -13819,7 +13819,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>6857.8636</v>
+        <v>8240.8984</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -16055,7 +16055,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>24142.64599715505</v>
+        <v>24382.84399715505</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -16391,7 +16391,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>1239.7588</v>
+        <v>1349.3228</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -16559,7 +16559,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>2024.4056</v>
+        <v>2374.1676</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -18795,7 +18795,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>16261.14613371266</v>
+        <v>15946.78173371266</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -19131,7 +19131,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>7275.049599999999</v>
+        <v>7602.056</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -19299,7 +19299,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>11593.5568</v>
+        <v>11606.1988</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -21535,7 +21535,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>10889.19873741109</v>
+        <v>10974.32153741109</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -21871,7 +21871,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>7989.744</v>
+        <v>7631.554</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -22039,7 +22039,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>7190.7696</v>
+        <v>6917.7024</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -24275,7 +24275,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>15409.52103157895</v>
+        <v>16573.42783157895</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -24611,7 +24611,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>5329.867200000001</v>
+        <v>5158.778799999999</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -24779,7 +24779,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>9737.7112</v>
+        <v>10730.5296</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -25181,7 +25181,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -25853,7 +25853,7 @@
         <v>31</v>
       </c>
       <c r="D48">
-        <v>435.7988351924992</v>
+        <v>365.0557938492175</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -25895,7 +25895,7 @@
         <v>5</v>
       </c>
       <c r="D51">
-        <v>2674.626865671642</v>
+        <v>4279.402985074627</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -25923,7 +25923,7 @@
         <v>7</v>
       </c>
       <c r="D53">
-        <v>2674.626865671642</v>
+        <v>1069.850746268657</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -26063,7 +26063,7 @@
         <v>5</v>
       </c>
       <c r="D63">
-        <v>20.51313432835832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -26091,7 +26091,7 @@
         <v>7</v>
       </c>
       <c r="D65">
-        <v>3365.081891794944</v>
+        <v>3385.595026123302</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -27015,7 +27015,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>16253.61616500711</v>
+        <v>15971.27816500711</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -27043,7 +27043,7 @@
         <v>43</v>
       </c>
       <c r="D133">
-        <v>643.1185576661974</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -27062,16 +27062,16 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C135" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>1584.262985074627</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -27093,13 +27093,13 @@
         <v>7</v>
       </c>
       <c r="B137" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C137" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1011.887468751711</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -27351,7 +27351,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>1074.57</v>
+        <v>1431.9172</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -27519,7 +27519,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>3484.1352</v>
+        <v>3559.1444</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -27594,10 +27594,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C173" t="s">
         <v>15</v>
@@ -27608,10 +27608,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B174" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C174" t="s">
         <v>15</v>
@@ -27622,10 +27622,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B175" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C175" t="s">
         <v>15</v>
@@ -27636,10 +27636,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C176" t="s">
         <v>15</v>
@@ -27650,10 +27650,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B177" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C177" t="s">
         <v>15</v>
@@ -27664,10 +27664,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B178" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C178" t="s">
         <v>15</v>
@@ -27678,10 +27678,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B179" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C179" t="s">
         <v>15</v>
@@ -27692,10 +27692,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B180" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C180" t="s">
         <v>15</v>
@@ -27706,10 +27706,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B181" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C181" t="s">
         <v>15</v>
@@ -27720,10 +27720,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B182" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C182" t="s">
         <v>15</v>
@@ -27734,10 +27734,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B183" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C183" t="s">
         <v>15</v>
@@ -27748,10 +27748,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B184" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C184" t="s">
         <v>15</v>
@@ -27762,10 +27762,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B185" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C185" t="s">
         <v>15</v>
@@ -27776,10 +27776,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B186" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C186" t="s">
         <v>15</v>
@@ -27790,10 +27790,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B187" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C187" t="s">
         <v>15</v>
@@ -27804,10 +27804,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C188" t="s">
         <v>15</v>
@@ -27818,10 +27818,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B189" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C189" t="s">
         <v>15</v>
@@ -27835,7 +27835,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C190" t="s">
         <v>15</v>
@@ -27846,10 +27846,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B191" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="C191" t="s">
         <v>15</v>
@@ -27860,57 +27860,29 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B192" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C192" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B193" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="C193" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D193">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
-      <c r="A194" t="s">
-        <v>29</v>
-      </c>
-      <c r="B194" t="s">
-        <v>4</v>
-      </c>
-      <c r="C194" t="s">
-        <v>4</v>
-      </c>
-      <c r="D194">
-        <v>1730</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
-      <c r="A195" t="s">
-        <v>30</v>
-      </c>
-      <c r="B195" t="s">
-        <v>42</v>
-      </c>
-      <c r="C195" t="s">
-        <v>44</v>
-      </c>
-      <c r="D195">
         <v>30000</v>
       </c>
     </row>
@@ -29755,7 +29727,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>8913.604302702701</v>
+        <v>9107.448302702702</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -30091,7 +30063,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>8314.222</v>
+        <v>7807.6992</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -30259,7 +30231,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>5852.4032</v>
+        <v>5539.7244</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -32495,7 +32467,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>89943.25082105263</v>
+        <v>88967.28842105264</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -32831,7 +32803,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>4686.8108</v>
+        <v>5328.1816</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -32999,7 +32971,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>4588.2032</v>
+        <v>4253.6116</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -35221,7 +35193,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>8084.025269416785</v>
+        <v>7676.110069416784</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -35557,7 +35529,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>143.276</v>
+        <v>90.17959999999999</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -35725,7 +35697,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>1434.4456</v>
+        <v>973.434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -37947,7 +37919,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>13563.62233399715</v>
+        <v>13564.46513399715</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -38283,7 +38255,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>288.2376</v>
+        <v>176.1452</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -38451,7 +38423,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>3432.7244</v>
+        <v>3321.4748</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -40673,7 +40645,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>4321.341588620198</v>
+        <v>3836.731588620198</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -41009,7 +40981,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>3351.8156</v>
+        <v>3715.0624</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -41177,7 +41149,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>3680.5076</v>
+        <v>3559.1444</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -43413,7 +43385,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>2916.402631578947</v>
+        <v>3175.711737665748</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -43749,7 +43721,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>6951.4144</v>
+        <v>4980.378493913199</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -43917,7 +43889,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>7438.552799999999</v>
+        <v>5726.826</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -46153,7 +46125,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>13040.43326088193</v>
+        <v>13135.66966088193</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -46489,7 +46461,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>5033.2016</v>
+        <v>5661.930399999999</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -46657,7 +46629,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>10052.9184</v>
+        <v>10776.8836</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -48893,7 +48865,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>5600.312293598861</v>
+        <v>5093.789493598862</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -49229,7 +49201,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>6011.6924</v>
+        <v>6122.0992</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -49397,7 +49369,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>6919.387999999999</v>
+        <v>6523.272</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -51619,7 +51591,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>8793.81506913229</v>
+        <v>9212.68666913229</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -51955,7 +51927,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>387.6879999999999</v>
+        <v>413.8148</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -52123,7 +52095,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>4601.688</v>
+        <v>5046.686400000001</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -54345,7 +54317,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>2631.202223044097</v>
+        <v>2613.503423044097</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -54681,7 +54653,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>1508.612</v>
+        <v>1311.3968</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -54849,7 +54821,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>1598.7916</v>
+        <v>1383.8776</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -57085,7 +57057,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>8487.955702987198</v>
+        <v>8358.164502987196</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -57421,7 +57393,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>1666.2156</v>
+        <v>1533.896</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -57589,7 +57561,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>2151.6684</v>
+        <v>1889.5576</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -59811,7 +59783,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>15049.88952546231</v>
+        <v>14704.34152546231</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -60147,7 +60119,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>3779.958</v>
+        <v>5071.1276</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -60315,7 +60287,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>2671.676</v>
+        <v>3617.2976</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -62537,7 +62509,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>44318.01671066855</v>
+        <v>43852.79111066856</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -62873,7 +62845,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>18313.2012</v>
+        <v>18952.8864</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -63041,7 +63013,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>6640.4212</v>
+        <v>6814.8808</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -65277,7 +65249,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>4317.084206543385</v>
+        <v>3947.937806543385</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -65613,7 +65585,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>2710.4448</v>
+        <v>2996.154</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -65781,7 +65753,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>3414.1828</v>
+        <v>3330.7456</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -68003,7 +67975,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>104180.3783362731</v>
+        <v>106069.9359362731</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -68339,7 +68311,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>17585.022</v>
+        <v>17270.6576</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -68507,7 +68479,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>41298.0428</v>
+        <v>42873.236</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -70743,7 +70715,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>42545.31411550498</v>
+        <v>42068.28931550498</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -71079,7 +71051,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>2106.1572</v>
+        <v>1774.094</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -71247,7 +71219,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>7385.4564</v>
+        <v>6576.368399999999</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -73483,7 +73455,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>35108.09224751066</v>
+        <v>35372.73144751066</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -73819,7 +73791,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>15118.1464</v>
+        <v>15777.216</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -73861,7 +73833,7 @@
         <v>4</v>
       </c>
       <c r="D158">
-        <v>45192.05494616081</v>
+        <v>45000.05494616081</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -73987,7 +73959,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>4374.132</v>
+        <v>5297.8408</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -74365,7 +74337,7 @@
         <v>4</v>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -76223,7 +76195,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>23821.15712261735</v>
+        <v>22169.26912261736</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -76559,7 +76531,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>27727.2772</v>
+        <v>29510.642</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -76727,7 +76699,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>21638.89</v>
+        <v>21770.3668</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -78963,7 +78935,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>17844.38378150782</v>
+        <v>18525.36618150782</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -79173,7 +79145,7 @@
         <v>4</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>800.2252472225613</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -79299,7 +79271,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>7287.6916</v>
+        <v>6254.418799999999</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -79341,7 +79313,7 @@
         <v>4</v>
       </c>
       <c r="D158">
-        <v>275.3325953507083</v>
+        <v>1075.55784257327</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -79467,7 +79439,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>2720.5584</v>
+        <v>2368.268</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -81703,7 +81675,7 @@
         <v>13</v>
       </c>
       <c r="D131">
-        <v>25610.86298264581</v>
+        <v>26736.0009826458</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -82039,7 +82011,7 @@
         <v>13</v>
       </c>
       <c r="D155">
-        <v>1989.008</v>
+        <v>1777.4652</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -82207,7 +82179,7 @@
         <v>13</v>
       </c>
       <c r="D167">
-        <v>2289.8876</v>
+        <v>3203.4828</v>
       </c>
     </row>
     <row r="168" spans="1:4">
